--- a/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/5.2-organic-fertiliser.xlsx
+++ b/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/5.2-organic-fertiliser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E913DBAC-EA2E-3441-9ABE-CA158C33DE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D485858-894E-9B48-9AC3-68495A050BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="760" windowWidth="50560" windowHeight="26020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="1520" windowWidth="50560" windowHeight="26020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.2.1.1 (purchased_untraced)" sheetId="1" r:id="rId1"/>
@@ -15981,19 +15981,24 @@
         <v>1</v>
       </c>
       <c r="AR71">
+        <f>$BZ$64</f>
         <v>0.02</v>
       </c>
       <c r="AS71">
+        <f>X71+X72+X74</f>
         <v>0.48773949</v>
       </c>
       <c r="AT71">
+        <f>X73+X75</f>
         <v>5.241817E-2</v>
       </c>
       <c r="AU71">
-        <v>1.7061210600000001</v>
+        <f>Y71+Y72+Y74</f>
+        <v>1.6414287625030253</v>
       </c>
       <c r="AV71">
-        <v>0.22558537000000001</v>
+        <f>Y73+Y75</f>
+        <v>0.20102491308955134</v>
       </c>
       <c r="AW71" t="s">
         <v>228</v>
@@ -16052,11 +16057,11 @@
       </c>
       <c r="BQ71">
         <f>SUM(BN71:BN74)</f>
-        <v>24141.080124162781</v>
+        <v>23380.878795239161</v>
       </c>
       <c r="BR71">
         <f>SUM(BO71:BO74)</f>
-        <v>6035.2700310406935</v>
+        <v>5845.2196988097894</v>
       </c>
       <c r="BS71">
         <f>IF(ISBLANK(AJ71), "", IF(AJ71="wet", $BZ$67, $BZ$68))</f>
@@ -16068,11 +16073,11 @@
       </c>
       <c r="BU71">
         <f>IF(ISBLANK(A71), "", BQ71*BS71*BT71/1000)</f>
-        <v>0.22761589831353482</v>
+        <v>0.2204482857836835</v>
       </c>
       <c r="BV71">
         <f>IF(ISBLANK(AT71), "", BR71*BS71*BT71/1000)</f>
-        <v>5.6903974578383684E-2</v>
+        <v>5.5112071445920875E-2</v>
       </c>
     </row>
     <row r="72" spans="1:78" x14ac:dyDescent="0.2">
@@ -16168,18 +16173,18 @@
       </c>
       <c r="BL72">
         <f>((AA71 * AU71 * 365) + (AC71 * AV71 * 281)  + (AC71 *AF71 * 84)) *BH72</f>
-        <v>9950.9205764920025</v>
+        <v>9548.6368372672259</v>
       </c>
       <c r="BM72">
         <v>0</v>
       </c>
       <c r="BN72">
         <f>((BK72 + BL72) * (1 - BI72 -BJ72)- BM72) *AH$11</f>
-        <v>9504.5921746779386</v>
+        <v>9205.2930726947034</v>
       </c>
       <c r="BO72">
         <f>((BK72 + BL72) * (1 - BI72 -BJ72)- BM72) *(1 - AH$11)</f>
-        <v>2376.1480436694837</v>
+        <v>2301.3232681736754</v>
       </c>
     </row>
     <row r="73" spans="1:78" x14ac:dyDescent="0.2">
@@ -16283,18 +16288,18 @@
       </c>
       <c r="BL73">
         <f>((AA71 * AU71 * 365) + (AC71 * AV71 * 281)  + (AC71 *AF71 * 84)) *BH73</f>
-        <v>14215.600823560002</v>
+        <v>13640.909767524608</v>
       </c>
       <c r="BM73">
         <v>0</v>
       </c>
       <c r="BN73">
         <f>((BK73 + BL73) * (1 - BI73 -BJ73)- BM73) *AH$11</f>
-        <v>11679.990383628803</v>
+        <v>11312.188107766153</v>
       </c>
       <c r="BO73">
         <f>((BK73 + BL73) * (1 - BI73 -BJ73)- BM73) *(1 - AH$11)</f>
-        <v>2919.9975959071999</v>
+        <v>2828.0470269415373</v>
       </c>
     </row>
     <row r="74" spans="1:78" x14ac:dyDescent="0.2">
@@ -16387,19 +16392,19 @@
       </c>
       <c r="BL74">
         <f>((AA71 * AU71 * 365) + (AC71 * AV71 * 281)  + (AC71 *AF71 * 84)) *BH74</f>
-        <v>4264.6802470680004</v>
+        <v>4092.2729302573821</v>
       </c>
       <c r="BM74">
         <f>(BL74+ BK74) *AQ71 *AR71</f>
-        <v>109.49990984652001</v>
+        <v>106.05176351030765</v>
       </c>
       <c r="BN74">
         <f>((BK74 + BL74) * (1 - BI74 -BJ74)- BM74) *AH$11</f>
-        <v>2956.4975658560406</v>
+        <v>2863.3976147783069</v>
       </c>
       <c r="BO74">
         <f>((BK74 + BL74) * (1 - BI74 -BJ74)- BM74) *(1 - AH$11)</f>
-        <v>739.12439146400993</v>
+        <v>715.84940369457649</v>
       </c>
     </row>
     <row r="75" spans="1:78" x14ac:dyDescent="0.2">
@@ -16500,7 +16505,7 @@
       </c>
       <c r="BL75">
         <f>((AA71 * AU71 * 365) + (AC71 * AV71 * 281)  + (AC71 *AF71 * 84)) *BH75</f>
-        <v>28431.201647120004</v>
+        <v>27281.819535049217</v>
       </c>
       <c r="BM75">
         <v>0</v>
@@ -17844,7 +17849,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C3:CH10 C16:E19 C12:E12 BW12:CH12 A3:A96 C77:CH85 C51:E54 C11:E11 G11:I11 G12:I12 C13:E13 G13:I13 C14:E14 G14:I14 C15:E15 G15:I15 G16:I18 C20:E20 G20:I20 C21:E25 G21:I25 C26:E30 G26:I30 C31:E35 G31:I35 C36:E40 G36:I38 C41:E45 G41:I45 C46:E50 G46:I50 C55:E55 G55:I55 G53:I54 C56:E60 G56:CH58 C61:E65 G61:I65 C66:E70 G66:I70 C71:E75 G73:I75 C91:CH91 C86:E90 G86:CH90 C92:E96 G92:CH96 G19:I19 CA19:CH19 CA20:CD20 CA21:CD25 G51:I51 BW51:CD51 G52:I52 BO52:CD52 BM52 AV51:BU51 Z51:AT51 R51:X51 L51:P51 G71:I71 BV71:CH71 BR71:BT71 G72:I72 BO72:CH72 BM72 K11:CH11 G39:I40 CA39:CD40 CA41:CD45 K12:BM12 K13:CH13 K14:CH14 K15:CH15 K16:CH18 K20:BW20 K19:BW19 K21:BW25 K26:CD30 K31:CD35 K36:CD38 K39:BW40 K41:BW45 K46:CD50 K55:CH55 K53:CD54 K52:BK52 K61:CH65 K66:L70 K73:L75 K71:L71 K72:L72 O66:O70 O71 C76:L76 N76:CH76 O73:O75 O72 Q66:CH70 R71 R73:R75 R72 G60:CH60 G59:R59 T59:CH59 X71 X73:X75 X72 AA71:BP71 AA73:CH75 AA72:BK72 BO12:BU12" numberStoredAsText="1"/>
+    <ignoredError sqref="C3:CH10 C16:E19 C12:E12 BW12:CH12 A3:A96 C77:CH85 C51:E54 C11:E11 G11:I11 G12:I12 C13:E13 G13:I13 C14:E14 G14:I14 C15:E15 G15:I15 G16:I18 C20:E20 G20:I20 C21:E25 G21:I25 C26:E30 G26:I30 C31:E35 G31:I35 C36:E40 G36:I38 C41:E45 G41:I45 C46:E50 G46:I50 C55:E55 G55:I55 G53:I54 C56:E60 G56:CH58 C61:E65 G61:I65 C66:E70 G66:I70 C71:E75 G73:I75 C91:CH91 C86:E90 G86:CH90 C92:E96 G92:CH96 G19:I19 CA19:CH19 CA20:CD20 CA21:CD25 G51:I51 BW51:CD51 G52:I52 BO52:CD52 BM52 AV51:BU51 Z51:AT51 R51:X51 L51:P51 G71:I71 BV71:CH71 BR71:BT71 G72:I72 BO72:CH72 BM72 K11:CH11 G39:I40 CA39:CD40 CA41:CD45 K12:BM12 K13:CH13 K14:CH14 K15:CH15 K16:CH18 K20:BW20 K19:BW19 K21:BW25 K26:CD30 K31:CD35 K36:CD38 K39:BW40 K41:BW45 K46:CD50 K55:CH55 K53:CD54 K52:BK52 K61:CH65 K66:L70 K73:L75 K71:L71 K72:L72 O66:O70 O71 C76:L76 N76:CH76 O73:O75 O72 Q67:CH70 R71 R73:R75 R72 G60:CH60 G59:R59 T59:CH59 X71 X73:X75 X72 AA71:AQ71 AA73:CH75 AA72:BK72 BO12:BU12 Q66:AT66 AV66:CH66 AW71:BP71" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/5.2-organic-fertiliser.xlsx
+++ b/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/5.2-organic-fertiliser.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D485858-894E-9B48-9AC3-68495A050BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159333E7-5453-5A4F-BBE6-2AA0B367FF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="1520" windowWidth="50560" windowHeight="26020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.2.1.1 (purchased_untraced)" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="5.2.1.1 (poultry)" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -60,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="483">
   <si>
     <t>Table A.2.1.4</t>
   </si>
@@ -1506,6 +1505,9 @@
   </si>
   <si>
     <t>0.3003 </t>
+  </si>
+  <si>
+    <t>Pasture range and paddock (free range)</t>
   </si>
 </sst>
 </file>
@@ -18399,7 +18401,7 @@
       </c>
       <c r="AD11">
         <f>AA13*(1 - V13 - U13)</f>
-        <v>20.582919359999998</v>
+        <v>21.257187408</v>
       </c>
       <c r="AE11">
         <f>AA14*(1 - V14 - U14)</f>
@@ -18445,7 +18447,7 @@
       </c>
       <c r="AR11">
         <f>SUM(AP11:AP15)</f>
-        <v>266.00820711536636</v>
+        <v>266.68247516336635</v>
       </c>
       <c r="AS11">
         <f>SUM(AQ11:AQ14)</f>
@@ -18461,7 +18463,7 @@
       </c>
       <c r="AV11">
         <f>IF(ISBLANK(D11), "", AR11*AT11*AU11/1000)</f>
-        <v>2.5080773813734541E-3</v>
+        <v>2.5144347658260257E-3</v>
       </c>
       <c r="AW11">
         <f>IF(ISBLANK(D11), "", AS11*AT11*AU11/1000)</f>
@@ -18548,7 +18550,7 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <f t="shared" ref="AA12:AA14" si="4">SUM(W12:Z12)</f>
+        <f>SUM(W12:Z12)</f>
         <v>422.67684800000001</v>
       </c>
       <c r="AF12" s="5" t="s">
@@ -18645,7 +18647,7 @@
       </c>
       <c r="U13">
         <f>VLOOKUP(S13, $AY$32:$BA$38, 3, FALSE)</f>
-        <v>0.02</v>
+        <v>1E-3</v>
       </c>
       <c r="V13">
         <f>VLOOKUP(S13, $AY$32:$AZ$38, 2, FALSE)</f>
@@ -18668,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="AA12:AA14" si="4">SUM(W13:Z13)</f>
         <v>35.487791999999999</v>
       </c>
       <c r="AF13" s="5" t="s">
@@ -18791,7 +18793,7 @@
       </c>
       <c r="AD14">
         <f>SUM(AB11:AD11)</f>
-        <v>431.84642033599999</v>
+        <v>432.52068838399998</v>
       </c>
       <c r="AF14" t="s">
         <v>425</v>
@@ -18841,14 +18843,14 @@
       </c>
       <c r="AJ15">
         <f>AG15*AB11+AH15*AC11+AI15*AD11</f>
-        <v>20.582919359999998</v>
+        <v>21.257187408</v>
       </c>
       <c r="AO15">
         <v>0</v>
       </c>
       <c r="AP15">
         <f>AJ15</f>
-        <v>20.582919359999998</v>
+        <v>21.257187408</v>
       </c>
       <c r="BD15" s="4" t="s">
         <v>372</v>
@@ -18872,7 +18874,7 @@
       </c>
       <c r="AJ16">
         <f>SUM(AJ11:AJ15)</f>
-        <v>431.84642033599999</v>
+        <v>432.52068838399998</v>
       </c>
       <c r="AY16" t="s">
         <v>3</v>
@@ -19000,7 +19002,7 @@
       </c>
       <c r="AD21">
         <f>AA23*(1 - V23 - U23)</f>
-        <v>20.582919359999998</v>
+        <v>21.257187408</v>
       </c>
       <c r="AE21">
         <f>AA24*(1 - V24 - U24)</f>
@@ -19046,7 +19048,7 @@
       </c>
       <c r="AR21">
         <f>SUM(AP21:AP25)</f>
-        <v>266.08123795537915</v>
+        <v>266.7555060033792</v>
       </c>
       <c r="AS21">
         <f>SUM(AQ21:AQ24)</f>
@@ -19062,7 +19064,7 @@
       </c>
       <c r="AV21">
         <f>IF(ISBLANK(D21), "", AR21*AT21*AU21/1000)</f>
-        <v>2.5087659578650031E-3</v>
+        <v>2.5151233423175751E-3</v>
       </c>
       <c r="AW21">
         <f>IF(ISBLANK(D21), "", AS21*AT21*AU21/1000)</f>
@@ -19233,7 +19235,7 @@
       </c>
       <c r="U23">
         <f>VLOOKUP(S23, $AY$32:$BA$38, 3, FALSE)</f>
-        <v>0.02</v>
+        <v>1E-3</v>
       </c>
       <c r="V23">
         <f>VLOOKUP(S23, $AY$32:$AZ$38, 2, FALSE)</f>
@@ -19376,7 +19378,7 @@
       </c>
       <c r="AD24">
         <f>SUM(AB21:AD21)</f>
-        <v>431.84642033599999</v>
+        <v>432.52068838399998</v>
       </c>
       <c r="AF24" t="s">
         <v>425</v>
@@ -19432,14 +19434,14 @@
       </c>
       <c r="AJ25">
         <f>AG25*AB21+AH25*AC21+AI25*AD21</f>
-        <v>20.582919359999998</v>
+        <v>21.257187408</v>
       </c>
       <c r="AO25">
         <v>0</v>
       </c>
       <c r="AP25">
         <f>AJ25</f>
-        <v>20.582919359999998</v>
+        <v>21.257187408</v>
       </c>
       <c r="AY25" s="5" t="s">
         <v>406</v>
@@ -19467,7 +19469,7 @@
       </c>
       <c r="AJ26">
         <f>SUM(AJ21:AJ25)</f>
-        <v>431.84642033599999</v>
+        <v>432.52068838399998</v>
       </c>
       <c r="AY26" s="5" t="s">
         <v>407</v>
@@ -19630,7 +19632,7 @@
       </c>
       <c r="AD31">
         <f>AA33*(1 - V33 - U33)</f>
-        <v>20.582919359999998</v>
+        <v>21.257187408</v>
       </c>
       <c r="AE31">
         <f>AA34*(1 - V34 - U34)</f>
@@ -19676,7 +19678,7 @@
       </c>
       <c r="AR31">
         <f>SUM(AP31:AP35)</f>
-        <v>266.00820711536636</v>
+        <v>266.68247516336635</v>
       </c>
       <c r="AS31">
         <f>SUM(AQ31:AQ34)</f>
@@ -19692,7 +19694,7 @@
       </c>
       <c r="AV31">
         <f>IF(ISBLANK(D31), "", AR31*AT31*AU31/1000)</f>
-        <v>2.0900644844778784E-3</v>
+        <v>2.0953623048550214E-3</v>
       </c>
       <c r="AW31">
         <f>IF(ISBLANK(D31), "", AS31*AT31*AU31/1000)</f>
@@ -19873,7 +19875,7 @@
       </c>
       <c r="U33">
         <f>VLOOKUP(S33, $AY$32:$BA$38, 3, FALSE)</f>
-        <v>0.02</v>
+        <v>1E-3</v>
       </c>
       <c r="V33">
         <f>VLOOKUP(S33, $AY$32:$AZ$38, 2, FALSE)</f>
@@ -20012,7 +20014,7 @@
       </c>
       <c r="AD34">
         <f>SUM(AB31:AD31)</f>
-        <v>431.84642033599999</v>
+        <v>432.52068838399998</v>
       </c>
       <c r="AF34" t="s">
         <v>425</v>
@@ -20050,7 +20052,7 @@
         <v>0.4</v>
       </c>
       <c r="BA34" s="5">
-        <v>0.02</v>
+        <v>1E-3</v>
       </c>
     </row>
     <row r="35" spans="1:53" x14ac:dyDescent="0.2">
@@ -20062,14 +20064,14 @@
       </c>
       <c r="AJ35">
         <f>AG35*AB31+AH35*AC31+AI35*AD31</f>
-        <v>20.582919359999998</v>
+        <v>21.257187408</v>
       </c>
       <c r="AO35">
         <v>0</v>
       </c>
       <c r="AP35">
         <f>AJ35</f>
-        <v>20.582919359999998</v>
+        <v>21.257187408</v>
       </c>
       <c r="AY35" s="5" t="s">
         <v>426</v>
@@ -20099,7 +20101,7 @@
       </c>
       <c r="AJ36">
         <f>SUM(AJ31:AJ35)</f>
-        <v>431.84642033599999</v>
+        <v>432.52068838399998</v>
       </c>
       <c r="AY36" s="5" t="s">
         <v>427</v>
@@ -20131,6 +20133,14 @@
       </c>
       <c r="BA38" s="5">
         <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="AY39" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="BA39" s="5">
+        <v>0.02</v>
       </c>
     </row>
     <row r="41" spans="1:53" x14ac:dyDescent="0.2">
@@ -20461,7 +20471,7 @@
       </c>
       <c r="U43">
         <f>VLOOKUP(S43, $AY$32:$BA$38, 3, FALSE)</f>
-        <v>0.02</v>
+        <v>1E-3</v>
       </c>
       <c r="V43">
         <f>VLOOKUP(S43, $AY$32:$AZ$38, 2, FALSE)</f>
@@ -20760,7 +20770,7 @@
       </c>
       <c r="AD51">
         <f>AA53*(1 - V53 - U53)</f>
-        <v>94.684118399999988</v>
+        <v>97.785839519999996</v>
       </c>
       <c r="AE51">
         <f>AA54*(1 - V54 - U54)</f>
@@ -20806,7 +20816,7 @@
       </c>
       <c r="AR51">
         <f>SUM(AP51:AP55)</f>
-        <v>378.45926564966396</v>
+        <v>381.56098676966394</v>
       </c>
       <c r="AS51">
         <f>SUM(AQ51:AQ54)</f>
@@ -20822,7 +20832,7 @@
       </c>
       <c r="AV51">
         <f>IF(ISBLANK(D51), "", AR51*AT51*AU51/1000)</f>
-        <v>3.5683302189825463E-3</v>
+        <v>3.5975750181139743E-3</v>
       </c>
       <c r="AW51">
         <f>IF(ISBLANK(D51), "", AS51*AT51*AU51/1000)</f>
@@ -20985,7 +20995,7 @@
       </c>
       <c r="U53">
         <f>VLOOKUP(S53, $AY$32:$BA$38, 3, FALSE)</f>
-        <v>0.02</v>
+        <v>1E-3</v>
       </c>
       <c r="V53">
         <f>VLOOKUP(S53, $AY$32:$AZ$38, 2, FALSE)</f>
@@ -21115,7 +21125,7 @@
       </c>
       <c r="AD54">
         <f>SUM(AB51:AD51)</f>
-        <v>589.85624431999997</v>
+        <v>592.95796543999995</v>
       </c>
       <c r="AF54" t="s">
         <v>425</v>
@@ -21156,14 +21166,14 @@
       </c>
       <c r="AJ55">
         <f>AG55*AB51+AH55*AC51+AI55*AD51</f>
-        <v>94.684118399999988</v>
+        <v>97.785839519999996</v>
       </c>
       <c r="AO55">
         <v>0</v>
       </c>
       <c r="AP55">
         <f>AJ55</f>
-        <v>94.684118399999988</v>
+        <v>97.785839519999996</v>
       </c>
     </row>
     <row r="56" spans="1:49" x14ac:dyDescent="0.2">
@@ -21184,7 +21194,7 @@
       </c>
       <c r="AJ56">
         <f>SUM(AJ51:AJ55)</f>
-        <v>589.85624431999997</v>
+        <v>592.95796543999995</v>
       </c>
     </row>
     <row r="61" spans="1:49" x14ac:dyDescent="0.2">
@@ -21279,7 +21289,7 @@
       </c>
       <c r="AD61">
         <f>AA63*(1 - V63 - U63)</f>
-        <v>14.732927999999998</v>
+        <v>15.215558399999999</v>
       </c>
       <c r="AE61">
         <f>AA64*(1 - V64 - U64)</f>
@@ -21325,7 +21335,7 @@
       </c>
       <c r="AR61">
         <f>SUM(AP61:AP65)</f>
-        <v>190.81681904640001</v>
+        <v>191.29944944640002</v>
       </c>
       <c r="AS61">
         <f>SUM(AQ61:AQ64)</f>
@@ -21341,7 +21351,7 @@
       </c>
       <c r="AV61">
         <f>IF(ISBLANK(D61), "", AR61*AT61*AU61/1000)</f>
-        <v>1.7991300081517717E-3</v>
+        <v>1.8036805233517716E-3</v>
       </c>
       <c r="AW61">
         <f>IF(ISBLANK(D61), "", AS61*AT61*AU61/1000)</f>
@@ -21500,7 +21510,7 @@
       </c>
       <c r="U63">
         <f>VLOOKUP(S63, $AY$32:$BA$38, 3, FALSE)</f>
-        <v>0.02</v>
+        <v>1E-3</v>
       </c>
       <c r="V63">
         <f>VLOOKUP(S63, $AY$32:$AZ$38, 2, FALSE)</f>
@@ -21628,7 +21638,7 @@
       </c>
       <c r="AD64">
         <f>SUM(AB61:AD61)</f>
-        <v>310.00876160000007</v>
+        <v>310.49139200000008</v>
       </c>
       <c r="AF64" t="s">
         <v>425</v>
@@ -21669,14 +21679,14 @@
       </c>
       <c r="AJ65">
         <f>AG65*AB61+AH65*AC61+AI65*AD61</f>
-        <v>14.732927999999998</v>
+        <v>15.215558399999999</v>
       </c>
       <c r="AO65">
         <v>0</v>
       </c>
       <c r="AP65">
         <f>AJ65</f>
-        <v>14.732927999999998</v>
+        <v>15.215558399999999</v>
       </c>
     </row>
     <row r="66" spans="32:42" x14ac:dyDescent="0.2">
@@ -21697,7 +21707,7 @@
       </c>
       <c r="AJ66">
         <f>SUM(AJ61:AJ65)</f>
-        <v>310.00876160000007</v>
+        <v>310.49139200000008</v>
       </c>
     </row>
   </sheetData>

--- a/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/5.2-organic-fertiliser.xlsx
+++ b/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/5.2-organic-fertiliser.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/5.2-organic-fertiliser-n2o/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159333E7-5453-5A4F-BBE6-2AA0B367FF6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C767587C-CB7A-1046-8BE0-561E8050B23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15900" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.2.1.1 (purchased_untraced)" sheetId="1" r:id="rId1"/>
-    <sheet name="5.2.1.1 (swine)" sheetId="2" r:id="rId2"/>
-    <sheet name="5.2.1.1 (feedlot)" sheetId="3" r:id="rId3"/>
-    <sheet name="5.2.1.1 (dairy)" sheetId="4" r:id="rId4"/>
-    <sheet name="5.2.1.1 (poultry)" sheetId="5" r:id="rId5"/>
+    <sheet name="5.2.1.1 (swine) (old)" sheetId="2" r:id="rId2"/>
+    <sheet name="5.2.1.1 (swine)" sheetId="6" r:id="rId3"/>
+    <sheet name="5.2.1.1 (feedlot)" sheetId="3" r:id="rId4"/>
+    <sheet name="5.2.1.1 (dairy)" sheetId="4" r:id="rId5"/>
+    <sheet name="5.2.1.1 (poultry)" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="573">
   <si>
     <t>Table A.2.1.4</t>
   </si>
@@ -1508,6 +1509,276 @@
   </si>
   <si>
     <t>Pasture range and paddock (free range)</t>
+  </si>
+  <si>
+    <t>Swine class</t>
+  </si>
+  <si>
+    <t>Number of poultry in each class j and subclass k</t>
+  </si>
+  <si>
+    <t>Duration of stay for each class and subclass of poultry</t>
+  </si>
+  <si>
+    <t>Feed Intake</t>
+  </si>
+  <si>
+    <t>Volatile solid production</t>
+  </si>
+  <si>
+    <t>Nitrogen waste production</t>
+  </si>
+  <si>
+    <t>Uncovered anaerobic lagoons</t>
+  </si>
+  <si>
+    <t>Outdoor</t>
+  </si>
+  <si>
+    <t>Covered/Digester</t>
+  </si>
+  <si>
+    <t>Deep Litter</t>
+  </si>
+  <si>
+    <t>Pit Storage &lt; 1 Month</t>
+  </si>
+  <si>
+    <t>Solid Storage</t>
+  </si>
+  <si>
+    <t>Solids separated</t>
+  </si>
+  <si>
+    <t>Solid separation rate</t>
+  </si>
+  <si>
+    <t>(true or false)</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>Dj</t>
+  </si>
+  <si>
+    <t>VSj</t>
+  </si>
+  <si>
+    <t>NWj</t>
+  </si>
+  <si>
+    <t>MMSjm=1T=1</t>
+  </si>
+  <si>
+    <t>MMSjm=5T=1</t>
+  </si>
+  <si>
+    <t>MMSjm=7T=1</t>
+  </si>
+  <si>
+    <t>MMSjm=8T=1</t>
+  </si>
+  <si>
+    <t>MMSjm=9T=1</t>
+  </si>
+  <si>
+    <t>MMSjm=4T=1</t>
+  </si>
+  <si>
+    <t>true/false</t>
+  </si>
+  <si>
+    <t>SSj</t>
+  </si>
+  <si>
+    <t>SNj</t>
+  </si>
+  <si>
+    <t>AEj</t>
+  </si>
+  <si>
+    <t>FNjm=1T=1</t>
+  </si>
+  <si>
+    <t>FNjm=5T=1</t>
+  </si>
+  <si>
+    <t>FNjm=7T=1</t>
+  </si>
+  <si>
+    <t>FNjm=8T=1</t>
+  </si>
+  <si>
+    <t>FNjm=9T=1</t>
+  </si>
+  <si>
+    <t>FNjm=4T=1</t>
+  </si>
+  <si>
+    <t>MNjm=1T=1</t>
+  </si>
+  <si>
+    <t>MNjm=5T=1</t>
+  </si>
+  <si>
+    <t>MNjm=7T=1</t>
+  </si>
+  <si>
+    <t>MNjm=8T=1</t>
+  </si>
+  <si>
+    <t>MNjm=9T=1</t>
+  </si>
+  <si>
+    <t>MNjm=4T=1</t>
+  </si>
+  <si>
+    <t>FracGASMm=1T=1</t>
+  </si>
+  <si>
+    <t>FracGASMm=5T=1</t>
+  </si>
+  <si>
+    <t>FracGASMm=7T=1</t>
+  </si>
+  <si>
+    <t>FracGASMm=8T=1</t>
+  </si>
+  <si>
+    <t>FracGASMm=9T=1</t>
+  </si>
+  <si>
+    <t>FracGASMm=4T=1</t>
+  </si>
+  <si>
+    <t>EFm=1</t>
+  </si>
+  <si>
+    <t>EFm=5</t>
+  </si>
+  <si>
+    <t>EFm=7</t>
+  </si>
+  <si>
+    <t>EFm=8</t>
+  </si>
+  <si>
+    <t>EFm=9</t>
+  </si>
+  <si>
+    <t>EFm=4</t>
+  </si>
+  <si>
+    <t>NTjm=1T=2</t>
+  </si>
+  <si>
+    <t>NTjm=5T=2</t>
+  </si>
+  <si>
+    <t>NTjm=7T=2</t>
+  </si>
+  <si>
+    <t>NTjm=8T=2</t>
+  </si>
+  <si>
+    <t>NTjm=9T=2</t>
+  </si>
+  <si>
+    <t>NTjm=4T=2</t>
+  </si>
+  <si>
+    <t>NTjmT=2</t>
+  </si>
+  <si>
+    <t>MNjm=1T=2</t>
+  </si>
+  <si>
+    <t>MNjm=4T=2</t>
+  </si>
+  <si>
+    <t>MNjm=13T=2</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>MAT</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>NSW</t>
+  </si>
+  <si>
+    <t>boars</t>
+  </si>
+  <si>
+    <t>sows</t>
+  </si>
+  <si>
+    <t>gilts</t>
+  </si>
+  <si>
+    <t>others</t>
+  </si>
+  <si>
+    <t>NT</t>
+  </si>
+  <si>
+    <t>QLD</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>Climate Zone</t>
+  </si>
+  <si>
+    <t>MNSoil</t>
+  </si>
+  <si>
+    <t>MNLeachm=5</t>
+  </si>
+  <si>
+    <t>Table A.1.6.1: Swine – Intake and manure characteristics derived from PigBal (2020-2024)</t>
+  </si>
+  <si>
+    <t>Class (j)</t>
+  </si>
+  <si>
+    <t>Feed Intake (Ij)</t>
+  </si>
+  <si>
+    <t>Volatile Solids (VSj)</t>
+  </si>
+  <si>
+    <t>Nitrogen in Waste (NWj)</t>
+  </si>
+  <si>
+    <t>Nitrogen separation rate</t>
+  </si>
+  <si>
+    <t>Annual nitrogen excretion</t>
+  </si>
+  <si>
+    <t>Allocation of manure to each MMS</t>
+  </si>
+  <si>
+    <t>Mass of nitrogen per system (stage 1)</t>
+  </si>
+  <si>
+    <t>Fraction of nitrogen per system (stage 1)</t>
+  </si>
+  <si>
+    <t>Mass of nitrogen per system (stage 2)</t>
+  </si>
+  <si>
+    <t>Instead of aggregate * fraction, sum nitrogen from relevant primary MMSs</t>
+  </si>
+  <si>
+    <t>𝐹𝑁𝑗𝑚 𝑇=1 = 𝑀𝑀𝑆𝑗𝑚 𝑇=1 × (1 − 𝑆𝑁𝑚)</t>
   </si>
 </sst>
 </file>
@@ -1517,7 +1788,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1557,8 +1828,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1577,6 +1854,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1590,7 +1873,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1604,6 +1887,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4467,6 +4751,4708 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{404C8614-4A45-BB4D-AA5C-D3B3E6290153}">
+  <dimension ref="A1:BU51"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BO2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="Z3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="4" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="U4" t="s">
+        <v>572</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>32</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>546</v>
+      </c>
+      <c r="B5" t="s">
+        <v>547</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>483</v>
+      </c>
+      <c r="F5" t="s">
+        <v>484</v>
+      </c>
+      <c r="G5" t="s">
+        <v>485</v>
+      </c>
+      <c r="H5" t="s">
+        <v>486</v>
+      </c>
+      <c r="I5" t="s">
+        <v>487</v>
+      </c>
+      <c r="J5" t="s">
+        <v>488</v>
+      </c>
+      <c r="K5" t="s">
+        <v>567</v>
+      </c>
+      <c r="S5" t="s">
+        <v>565</v>
+      </c>
+      <c r="T5" t="s">
+        <v>566</v>
+      </c>
+      <c r="U5" t="s">
+        <v>569</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>568</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>570</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>557</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="K6" t="s">
+        <v>489</v>
+      </c>
+      <c r="L6" t="s">
+        <v>490</v>
+      </c>
+      <c r="M6" t="s">
+        <v>491</v>
+      </c>
+      <c r="N6" t="s">
+        <v>492</v>
+      </c>
+      <c r="O6" t="s">
+        <v>493</v>
+      </c>
+      <c r="P6" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>495</v>
+      </c>
+      <c r="R6" t="s">
+        <v>496</v>
+      </c>
+      <c r="U6" t="s">
+        <v>489</v>
+      </c>
+      <c r="V6" t="s">
+        <v>490</v>
+      </c>
+      <c r="W6" t="s">
+        <v>491</v>
+      </c>
+      <c r="X6" t="s">
+        <v>492</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>493</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>494</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>489</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>490</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>491</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>492</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>493</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>494</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>489</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>490</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>491</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>492</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>493</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>494</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>489</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>490</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>491</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>492</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>493</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>494</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>489</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>490</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>491</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>492</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>493</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>494</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="AJ7" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="AM7" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="AQ7" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="AS7" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="AU7" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="AV7" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="AW7" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="AX7" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="AY7" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="AZ7" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="BA7" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="BB7" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="BC7" s="1"/>
+      <c r="BD7" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="BE7" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="BF7" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="BG7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BH7" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="BI7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="BJ7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="BK7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="BL7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BM7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BN7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BO7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="BP7" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>549</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>550</v>
+      </c>
+      <c r="F8">
+        <v>111</v>
+      </c>
+      <c r="G8">
+        <v>105</v>
+      </c>
+      <c r="H8">
+        <f>_xlfn.XLOOKUP($E8, $BR$48:$BR$51, BS$48:BS$51)</f>
+        <v>2.62</v>
+      </c>
+      <c r="I8">
+        <f t="shared" ref="I8:J8" si="0">_xlfn.XLOOKUP($E8, $BR$48:$BR$51, BT$48:BT$51)</f>
+        <v>0.4</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>0.25</v>
+      </c>
+      <c r="S8">
+        <v>0.25</v>
+      </c>
+      <c r="T8">
+        <v>536.13</v>
+      </c>
+      <c r="U8">
+        <f>K8*(1-$S8)</f>
+        <v>0.75</v>
+      </c>
+      <c r="V8">
+        <f>L8</f>
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <f t="shared" ref="W8:Y23" si="1">M8*(1-$S8)</f>
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <f>N8</f>
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <f>P8+(SUM(K8, M8, O8)*S8)</f>
+        <v>0.25</v>
+      </c>
+      <c r="AA8">
+        <f>$T8*U8</f>
+        <v>402.09749999999997</v>
+      </c>
+      <c r="AB8">
+        <f t="shared" ref="AB8:AF23" si="2">$T8*V8</f>
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="2"/>
+        <v>134.0325</v>
+      </c>
+      <c r="AG8">
+        <f>$BS$42</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH8">
+        <f>$BS$39</f>
+        <v>0.3</v>
+      </c>
+      <c r="AI8">
+        <f>$BS$43</f>
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <f>$BS$40</f>
+        <v>0.125</v>
+      </c>
+      <c r="AK8">
+        <f>$BS$44</f>
+        <v>0.25</v>
+      </c>
+      <c r="AL8">
+        <f>$BS$41</f>
+        <v>0.2</v>
+      </c>
+      <c r="AM8">
+        <f>$BS$33</f>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <f>$BS$30</f>
+        <v>0.02</v>
+      </c>
+      <c r="AO8">
+        <f>$BS$34</f>
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <f>$BS$31</f>
+        <v>0.01</v>
+      </c>
+      <c r="AQ8">
+        <f>$BS$35</f>
+        <v>2E-3</v>
+      </c>
+      <c r="AR8">
+        <f>$BS$32</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS8">
+        <f>AA8*(1-AG8-AM8)</f>
+        <v>180.94387499999996</v>
+      </c>
+      <c r="AT8">
+        <f t="shared" ref="AT8:AX23" si="3">AB8*(1-AH8-AN8)</f>
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <f>AD8*(1-AJ8-AP8)</f>
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <f t="shared" si="3"/>
+        <v>106.55583750000001</v>
+      </c>
+      <c r="AY8">
+        <f>SUM(AS8:AX8)</f>
+        <v>287.49971249999999</v>
+      </c>
+      <c r="AZ8">
+        <f>AU8</f>
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <f>AV8</f>
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <f>SUM(AS8:AT8,AW8:AX8)</f>
+        <v>287.49971249999999</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD8">
+        <f>IF(D8, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE8">
+        <f>$BS$13</f>
+        <v>0.02</v>
+      </c>
+      <c r="BF8">
+        <f>AB8*BD8*BE8</f>
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0.8</v>
+      </c>
+      <c r="BH8">
+        <f>(AZ8*(1-AG8-AM8)) + (BA8*(1-AL8-AR8)) +BB8-BF8</f>
+        <v>287.49971249999999</v>
+      </c>
+      <c r="BI8">
+        <f>BH8*BG8</f>
+        <v>229.99977000000001</v>
+      </c>
+      <c r="BJ8">
+        <f>BH8*(1-BG8)</f>
+        <v>57.499942499999982</v>
+      </c>
+      <c r="BK8">
+        <f>IF(ISBLANK(A8), "", IF(BC8="wet", $BS$8, $BS$9))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="BL8">
+        <f>IF(ISBLANK(A8), "", $BS$12)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM8">
+        <f>IF(ISBLANK(A8), "", BI8*BK8*BL8 / 1000)</f>
+        <v>2.1685692599999998E-3</v>
+      </c>
+      <c r="BN8">
+        <f>IF(ISBLANK(B8), "", BJ8*BK8*BL8 / 1000)</f>
+        <v>5.4214231499999984E-4</v>
+      </c>
+      <c r="BO8">
+        <f>SUM(BM8:BM11)</f>
+        <v>5.2543407425142866E-2</v>
+      </c>
+      <c r="BP8">
+        <f>SUM(BN8:BN11)</f>
+        <v>1.3135851856285713E-2</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>1</v>
+      </c>
+      <c r="BS8">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>549</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>551</v>
+      </c>
+      <c r="F9">
+        <v>222</v>
+      </c>
+      <c r="G9">
+        <v>103</v>
+      </c>
+      <c r="H9">
+        <f t="shared" ref="H9:H23" si="4">_xlfn.XLOOKUP($E9, $BR$48:$BR$51, BS$48:BS$51)</f>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I9">
+        <f t="shared" ref="I9:I23" si="5">_xlfn.XLOOKUP($E9, $BR$48:$BR$51, BT$48:BT$51)</f>
+        <v>0.46</v>
+      </c>
+      <c r="J9">
+        <f t="shared" ref="J9:J23" si="6">_xlfn.XLOOKUP($E9, $BR$48:$BR$51, BU$48:BU$51)</f>
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="b">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>0.25</v>
+      </c>
+      <c r="S9">
+        <v>0.25</v>
+      </c>
+      <c r="T9">
+        <v>1120.434</v>
+      </c>
+      <c r="U9">
+        <f t="shared" ref="U9:U23" si="7">K9*(1-$S9)</f>
+        <v>0.75</v>
+      </c>
+      <c r="V9">
+        <f t="shared" ref="V9:V23" si="8">L9</f>
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <f t="shared" ref="X9:X23" si="9">N9</f>
+        <v>0</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" ref="Z9:Z23" si="10">P9+(SUM(K9, M9, O9)*S9)</f>
+        <v>0.25</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" ref="AA9:AA23" si="11">$T9*U9</f>
+        <v>840.32549999999992</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="2"/>
+        <v>280.10849999999999</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" ref="AG9:AG23" si="12">$BS$42</f>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" ref="AH9:AH23" si="13">$BS$39</f>
+        <v>0.3</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" ref="AI9:AI23" si="14">$BS$43</f>
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" ref="AJ9:AJ23" si="15">$BS$40</f>
+        <v>0.125</v>
+      </c>
+      <c r="AK9">
+        <f t="shared" ref="AK9:AK23" si="16">$BS$44</f>
+        <v>0.25</v>
+      </c>
+      <c r="AL9">
+        <f t="shared" ref="AL9:AL23" si="17">$BS$41</f>
+        <v>0.2</v>
+      </c>
+      <c r="AM9">
+        <f t="shared" ref="AM9:AM23" si="18">$BS$33</f>
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <f t="shared" ref="AN9:AN23" si="19">$BS$30</f>
+        <v>0.02</v>
+      </c>
+      <c r="AO9">
+        <f t="shared" ref="AO9:AO23" si="20">$BS$34</f>
+        <v>0</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" ref="AP9:AP23" si="21">$BS$31</f>
+        <v>0.01</v>
+      </c>
+      <c r="AQ9">
+        <f t="shared" ref="AQ9:AQ23" si="22">$BS$35</f>
+        <v>2E-3</v>
+      </c>
+      <c r="AR9">
+        <f t="shared" ref="AR9:AR23" si="23">$BS$32</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS9">
+        <f t="shared" ref="AS9:AS23" si="24">AA9*(1-AG9-AM9)</f>
+        <v>378.14647499999995</v>
+      </c>
+      <c r="AT9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW9">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX9">
+        <f t="shared" si="3"/>
+        <v>222.68625750000001</v>
+      </c>
+      <c r="AY9">
+        <f t="shared" ref="AY9:AY23" si="25">SUM(AS9:AX9)</f>
+        <v>600.83273250000002</v>
+      </c>
+      <c r="AZ9">
+        <f t="shared" ref="AZ9:BA23" si="26">AU9</f>
+        <v>0</v>
+      </c>
+      <c r="BA9">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BB9">
+        <f t="shared" ref="BB9:BB23" si="27">SUM(AS9:AT9,AW9:AX9)</f>
+        <v>600.83273250000002</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD9">
+        <f t="shared" ref="BD9:BD23" si="28">IF(D9, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="BE9">
+        <f t="shared" ref="BE9:BE23" si="29">$BS$13</f>
+        <v>0.02</v>
+      </c>
+      <c r="BF9">
+        <f t="shared" ref="BF9:BF23" si="30">AB9*BD9*BE9</f>
+        <v>0</v>
+      </c>
+      <c r="BG9">
+        <v>0.8</v>
+      </c>
+      <c r="BH9">
+        <f t="shared" ref="BH9:BH23" si="31">(AZ9*(1-AG9-AM9)) + (BA9*(1-AL9-AR9)) +BB9-BF9</f>
+        <v>600.83273250000002</v>
+      </c>
+      <c r="BI9">
+        <f t="shared" ref="BI9:BI23" si="32">BH9*BG9</f>
+        <v>480.66618600000004</v>
+      </c>
+      <c r="BJ9">
+        <f t="shared" ref="BJ9:BJ23" si="33">BH9*(1-BG9)</f>
+        <v>120.16654649999998</v>
+      </c>
+      <c r="BK9">
+        <f>IF(ISBLANK(A9), "", IF(BC9="wet", $BS$8, $BS$9))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="BL9">
+        <f>IF(ISBLANK(A8), "", $BS$12)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM9">
+        <f>IF(ISBLANK(A8), "", BI9*BK9*BL9 / 1000)</f>
+        <v>4.5319954679999995E-3</v>
+      </c>
+      <c r="BN9">
+        <f t="shared" ref="BN9:BN23" si="34">IF(ISBLANK(B9), "", BJ9*BK9*BL9 / 1000)</f>
+        <v>1.1329988669999999E-3</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>2</v>
+      </c>
+      <c r="BS9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>549</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>552</v>
+      </c>
+      <c r="F10">
+        <v>333</v>
+      </c>
+      <c r="G10">
+        <v>200</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="5"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="6"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>3063.6</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="2"/>
+        <v>3063.6</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK10">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL10">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM10">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ10">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="3"/>
+        <v>2291.5727999999999</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="25"/>
+        <v>2291.5727999999999</v>
+      </c>
+      <c r="AZ10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <f t="shared" si="27"/>
+        <v>2291.5727999999999</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD10">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE10">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF10">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0.8</v>
+      </c>
+      <c r="BH10">
+        <f t="shared" si="31"/>
+        <v>2291.5727999999999</v>
+      </c>
+      <c r="BI10">
+        <f t="shared" si="32"/>
+        <v>1833.2582400000001</v>
+      </c>
+      <c r="BJ10">
+        <f t="shared" si="33"/>
+        <v>458.31455999999986</v>
+      </c>
+      <c r="BK10">
+        <f>IF(ISBLANK(A10), "", IF(BC10="wet", $BS$8, $BS$9))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="BL10">
+        <f t="shared" ref="BL10:BL23" si="35">IF(ISBLANK(A9), "", $BS$12)</f>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM10">
+        <f t="shared" ref="BM10:BM23" si="36">IF(ISBLANK(A9), "", BI10*BK10*BL10 / 1000)</f>
+        <v>1.7285006262857144E-2</v>
+      </c>
+      <c r="BN10">
+        <f t="shared" si="34"/>
+        <v>4.3212515657142844E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>549</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>553</v>
+      </c>
+      <c r="F11">
+        <v>444</v>
+      </c>
+      <c r="G11">
+        <v>365</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="4"/>
+        <v>1.71</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="5"/>
+        <v>0.39</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="6"/>
+        <v>3.1232876712328769E-2</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>5061.6000000000004</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="2"/>
+        <v>5061.6000000000004</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK11">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL11">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM11">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ11">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR11">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS11">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <f t="shared" si="3"/>
+        <v>3786.0768000000003</v>
+      </c>
+      <c r="AX11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <f t="shared" si="25"/>
+        <v>3786.0768000000003</v>
+      </c>
+      <c r="AZ11">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <f t="shared" si="27"/>
+        <v>3786.0768000000003</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD11">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE11">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF11">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0.8</v>
+      </c>
+      <c r="BH11">
+        <f t="shared" si="31"/>
+        <v>3786.0768000000003</v>
+      </c>
+      <c r="BI11">
+        <f t="shared" si="32"/>
+        <v>3028.8614400000006</v>
+      </c>
+      <c r="BJ11">
+        <f t="shared" si="33"/>
+        <v>757.21535999999992</v>
+      </c>
+      <c r="BK11">
+        <f>IF(ISBLANK(A11), "", IF(BC11="wet", $BS$8, $BS$9))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="BL11">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM11">
+        <f t="shared" si="36"/>
+        <v>2.8557836434285718E-2</v>
+      </c>
+      <c r="BN11">
+        <f t="shared" si="34"/>
+        <v>7.1394591085714287E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>554</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>550</v>
+      </c>
+      <c r="F12">
+        <v>105</v>
+      </c>
+      <c r="G12">
+        <v>75</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="4"/>
+        <v>2.62</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="6"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K12">
+        <v>0.2</v>
+      </c>
+      <c r="L12">
+        <v>0.1</v>
+      </c>
+      <c r="M12">
+        <v>0.2</v>
+      </c>
+      <c r="N12">
+        <v>0.2</v>
+      </c>
+      <c r="O12">
+        <v>0.2</v>
+      </c>
+      <c r="P12">
+        <v>0.1</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>0.25</v>
+      </c>
+      <c r="S12">
+        <v>0.25</v>
+      </c>
+      <c r="T12">
+        <v>362.25</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="7"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="8"/>
+        <v>0.1</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="1"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="X12">
+        <f t="shared" si="9"/>
+        <v>0.2</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="1"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="10"/>
+        <v>0.25</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="11"/>
+        <v>54.337500000000006</v>
+      </c>
+      <c r="AB12">
+        <f>$T12*V12</f>
+        <v>36.225000000000001</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="2"/>
+        <v>54.337500000000006</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="2"/>
+        <v>72.45</v>
+      </c>
+      <c r="AE12">
+        <f t="shared" si="2"/>
+        <v>54.337500000000006</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="2"/>
+        <v>90.5625</v>
+      </c>
+      <c r="AG12">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH12">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI12">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK12">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL12">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM12">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO12">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ12">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR12">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS12">
+        <f t="shared" si="24"/>
+        <v>24.451875000000001</v>
+      </c>
+      <c r="AT12">
+        <f>AB12*(1-AH12-AN12)</f>
+        <v>24.632999999999999</v>
+      </c>
+      <c r="AU12">
+        <f t="shared" si="3"/>
+        <v>54.337500000000006</v>
+      </c>
+      <c r="AV12">
+        <f>AD12*(1-AJ12-AP12)</f>
+        <v>62.669250000000005</v>
+      </c>
+      <c r="AW12">
+        <f t="shared" si="3"/>
+        <v>40.644450000000006</v>
+      </c>
+      <c r="AX12">
+        <f t="shared" si="3"/>
+        <v>71.99718750000001</v>
+      </c>
+      <c r="AY12">
+        <f t="shared" si="25"/>
+        <v>278.73326250000002</v>
+      </c>
+      <c r="AZ12">
+        <f t="shared" si="26"/>
+        <v>54.337500000000006</v>
+      </c>
+      <c r="BA12">
+        <f t="shared" si="26"/>
+        <v>62.669250000000005</v>
+      </c>
+      <c r="BB12">
+        <f t="shared" si="27"/>
+        <v>161.72651250000001</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD12">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE12">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF12">
+        <f t="shared" si="30"/>
+        <v>0.72450000000000003</v>
+      </c>
+      <c r="BG12">
+        <v>0.5</v>
+      </c>
+      <c r="BH12">
+        <f t="shared" si="31"/>
+        <v>235.27594125000002</v>
+      </c>
+      <c r="BI12">
+        <f t="shared" si="32"/>
+        <v>117.63797062500001</v>
+      </c>
+      <c r="BJ12">
+        <f t="shared" si="33"/>
+        <v>117.63797062500001</v>
+      </c>
+      <c r="BK12">
+        <f>IF(ISBLANK(A12), "", IF(BC12="wet", $BS$8, $BS$9))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BL12">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM12">
+        <f t="shared" si="36"/>
+        <v>9.2429834062500004E-4</v>
+      </c>
+      <c r="BN12">
+        <f t="shared" si="34"/>
+        <v>9.2429834062500004E-4</v>
+      </c>
+      <c r="BO12">
+        <f>SUM(BM12:BM15)</f>
+        <v>2.5087208619887971E-2</v>
+      </c>
+      <c r="BP12">
+        <f>SUM(BN12:BN15)</f>
+        <v>2.5087208619887971E-2</v>
+      </c>
+      <c r="BR12" t="s">
+        <v>3</v>
+      </c>
+      <c r="BS12">
+        <f>44/28</f>
+        <v>1.5714285714285714</v>
+      </c>
+    </row>
+    <row r="13" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>554</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>551</v>
+      </c>
+      <c r="F13">
+        <v>245</v>
+      </c>
+      <c r="G13">
+        <v>290</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="4"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="5"/>
+        <v>0.46</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="6"/>
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="K13">
+        <v>0.2</v>
+      </c>
+      <c r="L13">
+        <v>0.1</v>
+      </c>
+      <c r="M13">
+        <v>0.2</v>
+      </c>
+      <c r="N13">
+        <v>0.2</v>
+      </c>
+      <c r="O13">
+        <v>0.2</v>
+      </c>
+      <c r="P13">
+        <v>0.1</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>0.25</v>
+      </c>
+      <c r="S13">
+        <v>0.25</v>
+      </c>
+      <c r="T13">
+        <v>3481.4500000000003</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="7"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="8"/>
+        <v>0.1</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="1"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="9"/>
+        <v>0.2</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="1"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="10"/>
+        <v>0.25</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="11"/>
+        <v>522.21750000000009</v>
+      </c>
+      <c r="AB13">
+        <f t="shared" si="2"/>
+        <v>348.14500000000004</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="2"/>
+        <v>522.21750000000009</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="2"/>
+        <v>696.29000000000008</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="2"/>
+        <v>522.21750000000009</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="2"/>
+        <v>870.36250000000007</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK13">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL13">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM13">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO13">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ13">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR13">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS13">
+        <f t="shared" si="24"/>
+        <v>234.99787500000002</v>
+      </c>
+      <c r="AT13">
+        <f t="shared" si="3"/>
+        <v>236.73859999999999</v>
+      </c>
+      <c r="AU13">
+        <f t="shared" si="3"/>
+        <v>522.21750000000009</v>
+      </c>
+      <c r="AV13">
+        <f t="shared" si="3"/>
+        <v>602.29085000000009</v>
+      </c>
+      <c r="AW13">
+        <f t="shared" si="3"/>
+        <v>390.61869000000007</v>
+      </c>
+      <c r="AX13">
+        <f t="shared" si="3"/>
+        <v>691.93818750000014</v>
+      </c>
+      <c r="AY13">
+        <f t="shared" si="25"/>
+        <v>2678.8017025000004</v>
+      </c>
+      <c r="AZ13">
+        <f t="shared" si="26"/>
+        <v>522.21750000000009</v>
+      </c>
+      <c r="BA13">
+        <f t="shared" si="26"/>
+        <v>602.29085000000009</v>
+      </c>
+      <c r="BB13">
+        <f t="shared" si="27"/>
+        <v>1554.2933525000003</v>
+      </c>
+      <c r="BC13" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD13">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE13">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF13">
+        <f t="shared" si="30"/>
+        <v>6.9629000000000012</v>
+      </c>
+      <c r="BG13">
+        <v>0.5</v>
+      </c>
+      <c r="BH13">
+        <f t="shared" si="31"/>
+        <v>2261.1495532500007</v>
+      </c>
+      <c r="BI13">
+        <f t="shared" si="32"/>
+        <v>1130.5747766250004</v>
+      </c>
+      <c r="BJ13">
+        <f t="shared" si="33"/>
+        <v>1130.5747766250004</v>
+      </c>
+      <c r="BK13">
+        <f>IF(ISBLANK(A13), "", IF(BC13="wet", $BS$8, $BS$9))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BL13">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM13">
+        <f t="shared" si="36"/>
+        <v>8.8830875306250036E-3</v>
+      </c>
+      <c r="BN13">
+        <f t="shared" si="34"/>
+        <v>8.8830875306250036E-3</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>84</v>
+      </c>
+      <c r="BS13">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="14" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>554</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>552</v>
+      </c>
+      <c r="F14">
+        <v>434</v>
+      </c>
+      <c r="G14">
+        <v>280</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="5"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="6"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K14">
+        <v>0.2</v>
+      </c>
+      <c r="L14">
+        <v>0.1</v>
+      </c>
+      <c r="M14">
+        <v>0.2</v>
+      </c>
+      <c r="N14">
+        <v>0.2</v>
+      </c>
+      <c r="O14">
+        <v>0.2</v>
+      </c>
+      <c r="P14">
+        <v>0.1</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>0.25</v>
+      </c>
+      <c r="S14">
+        <v>0.25</v>
+      </c>
+      <c r="T14">
+        <v>5589.92</v>
+      </c>
+      <c r="U14">
+        <f t="shared" si="7"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="8"/>
+        <v>0.1</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="1"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="9"/>
+        <v>0.2</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="1"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="10"/>
+        <v>0.25</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="11"/>
+        <v>838.48800000000017</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="2"/>
+        <v>558.99200000000008</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="2"/>
+        <v>838.48800000000017</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="2"/>
+        <v>1117.9840000000002</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" si="2"/>
+        <v>838.48800000000017</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="2"/>
+        <v>1397.48</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK14">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL14">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM14">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO14">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR14">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS14">
+        <f t="shared" si="24"/>
+        <v>377.31960000000004</v>
+      </c>
+      <c r="AT14">
+        <f t="shared" si="3"/>
+        <v>380.11456000000004</v>
+      </c>
+      <c r="AU14">
+        <f t="shared" si="3"/>
+        <v>838.48800000000017</v>
+      </c>
+      <c r="AV14">
+        <f t="shared" si="3"/>
+        <v>967.05616000000009</v>
+      </c>
+      <c r="AW14">
+        <f t="shared" si="3"/>
+        <v>627.18902400000013</v>
+      </c>
+      <c r="AX14">
+        <f t="shared" si="3"/>
+        <v>1110.9966000000002</v>
+      </c>
+      <c r="AY14">
+        <f t="shared" si="25"/>
+        <v>4301.1639440000008</v>
+      </c>
+      <c r="AZ14">
+        <f t="shared" si="26"/>
+        <v>838.48800000000017</v>
+      </c>
+      <c r="BA14">
+        <f t="shared" si="26"/>
+        <v>967.05616000000009</v>
+      </c>
+      <c r="BB14">
+        <f t="shared" si="27"/>
+        <v>2495.6197840000004</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD14">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE14">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF14">
+        <f t="shared" si="30"/>
+        <v>11.179840000000002</v>
+      </c>
+      <c r="BG14">
+        <v>0.5</v>
+      </c>
+      <c r="BH14">
+        <f t="shared" si="31"/>
+        <v>3630.5691912000007</v>
+      </c>
+      <c r="BI14">
+        <f t="shared" si="32"/>
+        <v>1815.2845956000003</v>
+      </c>
+      <c r="BJ14">
+        <f t="shared" si="33"/>
+        <v>1815.2845956000003</v>
+      </c>
+      <c r="BK14">
+        <f>IF(ISBLANK(A14), "", IF(BC14="wet", $BS$8, $BS$9))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BL14">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM14">
+        <f t="shared" si="36"/>
+        <v>1.4262950394000003E-2</v>
+      </c>
+      <c r="BN14">
+        <f t="shared" si="34"/>
+        <v>1.4262950394000003E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>554</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>553</v>
+      </c>
+      <c r="F15">
+        <v>44</v>
+      </c>
+      <c r="G15">
+        <v>290</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="4"/>
+        <v>1.71</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="5"/>
+        <v>0.39</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="6"/>
+        <v>3.1232876712328769E-2</v>
+      </c>
+      <c r="K15">
+        <v>0.2</v>
+      </c>
+      <c r="L15">
+        <v>0.1</v>
+      </c>
+      <c r="M15">
+        <v>0.2</v>
+      </c>
+      <c r="N15">
+        <v>0.2</v>
+      </c>
+      <c r="O15">
+        <v>0.2</v>
+      </c>
+      <c r="P15">
+        <v>0.1</v>
+      </c>
+      <c r="Q15" t="b">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>0.25</v>
+      </c>
+      <c r="S15">
+        <v>0.25</v>
+      </c>
+      <c r="T15">
+        <v>398.53150684931506</v>
+      </c>
+      <c r="U15">
+        <f t="shared" si="7"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="8"/>
+        <v>0.1</v>
+      </c>
+      <c r="W15">
+        <f t="shared" si="1"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="X15">
+        <f t="shared" si="9"/>
+        <v>0.2</v>
+      </c>
+      <c r="Y15">
+        <f t="shared" si="1"/>
+        <v>0.15000000000000002</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="10"/>
+        <v>0.25</v>
+      </c>
+      <c r="AA15">
+        <f t="shared" si="11"/>
+        <v>59.779726027397267</v>
+      </c>
+      <c r="AB15">
+        <f t="shared" si="2"/>
+        <v>39.853150684931506</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="2"/>
+        <v>59.779726027397267</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="2"/>
+        <v>79.706301369863013</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="2"/>
+        <v>59.779726027397267</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="2"/>
+        <v>99.632876712328766</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ15">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK15">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL15">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM15">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO15">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP15">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ15">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR15">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS15">
+        <f t="shared" si="24"/>
+        <v>26.900876712328767</v>
+      </c>
+      <c r="AT15">
+        <f t="shared" si="3"/>
+        <v>27.100142465753422</v>
+      </c>
+      <c r="AU15">
+        <f t="shared" si="3"/>
+        <v>59.779726027397267</v>
+      </c>
+      <c r="AV15">
+        <f t="shared" si="3"/>
+        <v>68.945950684931503</v>
+      </c>
+      <c r="AW15">
+        <f t="shared" si="3"/>
+        <v>44.715235068493158</v>
+      </c>
+      <c r="AX15">
+        <f t="shared" si="3"/>
+        <v>79.208136986301369</v>
+      </c>
+      <c r="AY15">
+        <f t="shared" si="25"/>
+        <v>306.65006794520548</v>
+      </c>
+      <c r="AZ15">
+        <f t="shared" si="26"/>
+        <v>59.779726027397267</v>
+      </c>
+      <c r="BA15">
+        <f t="shared" si="26"/>
+        <v>68.945950684931503</v>
+      </c>
+      <c r="BB15">
+        <f t="shared" si="27"/>
+        <v>177.9243912328767</v>
+      </c>
+      <c r="BC15" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD15">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE15">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF15">
+        <f t="shared" si="30"/>
+        <v>0.7970630136986302</v>
+      </c>
+      <c r="BG15">
+        <v>0.5</v>
+      </c>
+      <c r="BH15">
+        <f t="shared" si="31"/>
+        <v>258.8402357260274</v>
+      </c>
+      <c r="BI15">
+        <f t="shared" si="32"/>
+        <v>129.4201178630137</v>
+      </c>
+      <c r="BJ15">
+        <f t="shared" si="33"/>
+        <v>129.4201178630137</v>
+      </c>
+      <c r="BK15">
+        <f>IF(ISBLANK(A15), "", IF(BC15="wet", $BS$8, $BS$9))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BL15">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM15">
+        <f t="shared" si="36"/>
+        <v>1.0168723546379649E-3</v>
+      </c>
+      <c r="BN15">
+        <f t="shared" si="34"/>
+        <v>1.0168723546379649E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>555</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>550</v>
+      </c>
+      <c r="F16">
+        <v>1000</v>
+      </c>
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="4"/>
+        <v>2.62</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="6"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K16">
+        <v>0.3</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0.3</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0.4</v>
+      </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>4600</v>
+      </c>
+      <c r="U16">
+        <f t="shared" si="7"/>
+        <v>0.3</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <f t="shared" si="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="Y16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="10"/>
+        <v>0.4</v>
+      </c>
+      <c r="AA16">
+        <f t="shared" si="11"/>
+        <v>1380</v>
+      </c>
+      <c r="AB16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="2"/>
+        <v>1380</v>
+      </c>
+      <c r="AE16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="2"/>
+        <v>1840</v>
+      </c>
+      <c r="AG16">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH16">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI16">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ16">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK16">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL16">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM16">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN16">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO16">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ16">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR16">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS16">
+        <f t="shared" si="24"/>
+        <v>620.99999999999989</v>
+      </c>
+      <c r="AT16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV16">
+        <f t="shared" si="3"/>
+        <v>1193.7</v>
+      </c>
+      <c r="AW16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX16">
+        <f t="shared" si="3"/>
+        <v>1462.8000000000002</v>
+      </c>
+      <c r="AY16">
+        <f t="shared" si="25"/>
+        <v>3277.5</v>
+      </c>
+      <c r="AZ16">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BA16">
+        <f t="shared" si="26"/>
+        <v>1193.7</v>
+      </c>
+      <c r="BB16">
+        <f t="shared" si="27"/>
+        <v>2083.8000000000002</v>
+      </c>
+      <c r="BC16" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD16">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE16">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF16">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG16">
+        <v>1</v>
+      </c>
+      <c r="BH16">
+        <f t="shared" si="31"/>
+        <v>3032.7915000000003</v>
+      </c>
+      <c r="BI16">
+        <f t="shared" si="32"/>
+        <v>3032.7915000000003</v>
+      </c>
+      <c r="BJ16">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BK16">
+        <f>IF(ISBLANK(A16), "", IF(BC16="wet", $BS$8, $BS$9))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="BL16">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM16">
+        <f t="shared" si="36"/>
+        <v>2.8594891285714286E-2</v>
+      </c>
+      <c r="BN16">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BO16">
+        <f>SUM(BM16:BM19)</f>
+        <v>6.1823095532204504E-2</v>
+      </c>
+      <c r="BP16">
+        <f>SUM(BN16:BN19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>555</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>551</v>
+      </c>
+      <c r="F17">
+        <v>233</v>
+      </c>
+      <c r="G17">
+        <v>100</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="4"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="5"/>
+        <v>0.46</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="6"/>
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="K17">
+        <v>0.3</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0.3</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0.4</v>
+      </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>1141.7</v>
+      </c>
+      <c r="U17">
+        <f t="shared" si="7"/>
+        <v>0.3</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <f t="shared" si="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="Y17">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="10"/>
+        <v>0.4</v>
+      </c>
+      <c r="AA17">
+        <f t="shared" si="11"/>
+        <v>342.51</v>
+      </c>
+      <c r="AB17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="2"/>
+        <v>342.51</v>
+      </c>
+      <c r="AE17">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <f t="shared" si="2"/>
+        <v>456.68000000000006</v>
+      </c>
+      <c r="AG17">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH17">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI17">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK17">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL17">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM17">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO17">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ17">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR17">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS17">
+        <f t="shared" si="24"/>
+        <v>154.12949999999998</v>
+      </c>
+      <c r="AT17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <f t="shared" si="3"/>
+        <v>296.27114999999998</v>
+      </c>
+      <c r="AW17">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <f t="shared" si="3"/>
+        <v>363.06060000000008</v>
+      </c>
+      <c r="AY17">
+        <f t="shared" si="25"/>
+        <v>813.46125000000006</v>
+      </c>
+      <c r="AZ17">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <f t="shared" si="26"/>
+        <v>296.27114999999998</v>
+      </c>
+      <c r="BB17">
+        <f t="shared" si="27"/>
+        <v>517.19010000000003</v>
+      </c>
+      <c r="BC17" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD17">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE17">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF17">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>1</v>
+      </c>
+      <c r="BH17">
+        <f t="shared" si="31"/>
+        <v>752.72566425000002</v>
+      </c>
+      <c r="BI17">
+        <f t="shared" si="32"/>
+        <v>752.72566425000002</v>
+      </c>
+      <c r="BJ17">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <f>IF(ISBLANK(A17), "", IF(BC17="wet", $BS$8, $BS$9))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="BL17">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM17">
+        <f t="shared" si="36"/>
+        <v>7.0971276915000004E-3</v>
+      </c>
+      <c r="BN17">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>555</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>552</v>
+      </c>
+      <c r="F18">
+        <v>923</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="5"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="6"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0.5</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0.5</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>4245.8</v>
+      </c>
+      <c r="U18">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="X18">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z18">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <f t="shared" si="2"/>
+        <v>2122.9</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <f t="shared" si="2"/>
+        <v>2122.9</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH18">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI18">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK18">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL18">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM18">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO18">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ18">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR18">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS18">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <f t="shared" si="3"/>
+        <v>2122.9</v>
+      </c>
+      <c r="AV18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <f t="shared" si="3"/>
+        <v>1587.9292</v>
+      </c>
+      <c r="AX18">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <f t="shared" si="25"/>
+        <v>3710.8292000000001</v>
+      </c>
+      <c r="AZ18">
+        <f t="shared" si="26"/>
+        <v>2122.9</v>
+      </c>
+      <c r="BA18">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <f t="shared" si="27"/>
+        <v>1587.9292</v>
+      </c>
+      <c r="BC18" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD18">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE18">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF18">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>1</v>
+      </c>
+      <c r="BH18">
+        <f t="shared" si="31"/>
+        <v>2543.2341999999999</v>
+      </c>
+      <c r="BI18">
+        <f t="shared" si="32"/>
+        <v>2543.2341999999999</v>
+      </c>
+      <c r="BJ18">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <f>IF(ISBLANK(A18), "", IF(BC18="wet", $BS$8, $BS$9))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="BL18">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM18">
+        <f>IF(ISBLANK(A17), "", BI18*BK18*BL18 / 1000)</f>
+        <v>2.3979065314285713E-2</v>
+      </c>
+      <c r="BN18">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BR18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>555</v>
+      </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>553</v>
+      </c>
+      <c r="F19">
+        <v>122</v>
+      </c>
+      <c r="G19">
+        <v>100</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="4"/>
+        <v>1.71</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="5"/>
+        <v>0.39</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="6"/>
+        <v>3.1232876712328769E-2</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0.5</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0.5</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>381.04109589041099</v>
+      </c>
+      <c r="U19">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="X19">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <f t="shared" si="2"/>
+        <v>190.52054794520549</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <f t="shared" si="2"/>
+        <v>190.52054794520549</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI19">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK19">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL19">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM19">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO19">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP19">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ19">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR19">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS19">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU19">
+        <f t="shared" si="3"/>
+        <v>190.52054794520549</v>
+      </c>
+      <c r="AV19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW19">
+        <f t="shared" si="3"/>
+        <v>142.50936986301372</v>
+      </c>
+      <c r="AX19">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY19">
+        <f t="shared" si="25"/>
+        <v>333.02991780821924</v>
+      </c>
+      <c r="AZ19">
+        <f t="shared" si="26"/>
+        <v>190.52054794520549</v>
+      </c>
+      <c r="BA19">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BB19">
+        <f t="shared" si="27"/>
+        <v>142.50936986301372</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD19">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="BE19">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF19">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG19">
+        <v>1</v>
+      </c>
+      <c r="BH19">
+        <f t="shared" si="31"/>
+        <v>228.24361643835618</v>
+      </c>
+      <c r="BI19">
+        <f t="shared" si="32"/>
+        <v>228.24361643835618</v>
+      </c>
+      <c r="BJ19">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="BK19">
+        <f>IF(ISBLANK(A19), "", IF(BC19="wet", $BS$8, $BS$9))</f>
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="BL19">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM19">
+        <f t="shared" si="36"/>
+        <v>2.1520112407045012E-3</v>
+      </c>
+      <c r="BN19">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="BR19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>556</v>
+      </c>
+      <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>550</v>
+      </c>
+      <c r="F20">
+        <v>750</v>
+      </c>
+      <c r="G20">
+        <v>200</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="4"/>
+        <v>2.62</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="6"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K20">
+        <v>0.3</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0.3</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0.4</v>
+      </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>6900</v>
+      </c>
+      <c r="U20">
+        <f t="shared" si="7"/>
+        <v>0.3</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <f t="shared" si="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="Y20">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="10"/>
+        <v>0.4</v>
+      </c>
+      <c r="AA20">
+        <f t="shared" si="11"/>
+        <v>2070</v>
+      </c>
+      <c r="AB20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="2"/>
+        <v>2070</v>
+      </c>
+      <c r="AE20">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="2"/>
+        <v>2760</v>
+      </c>
+      <c r="AG20">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH20">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI20">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK20">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL20">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM20">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO20">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ20">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR20">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS20">
+        <f t="shared" si="24"/>
+        <v>931.49999999999989</v>
+      </c>
+      <c r="AT20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <f t="shared" si="3"/>
+        <v>1790.55</v>
+      </c>
+      <c r="AW20">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <f t="shared" si="3"/>
+        <v>2194.2000000000003</v>
+      </c>
+      <c r="AY20">
+        <f t="shared" si="25"/>
+        <v>4916.25</v>
+      </c>
+      <c r="AZ20">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <f t="shared" si="26"/>
+        <v>1790.55</v>
+      </c>
+      <c r="BB20">
+        <f t="shared" si="27"/>
+        <v>3125.7000000000003</v>
+      </c>
+      <c r="BC20" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD20">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF20">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0.75</v>
+      </c>
+      <c r="BH20">
+        <f t="shared" si="31"/>
+        <v>4549.1872500000009</v>
+      </c>
+      <c r="BI20">
+        <f t="shared" si="32"/>
+        <v>3411.8904375000006</v>
+      </c>
+      <c r="BJ20">
+        <f t="shared" si="33"/>
+        <v>1137.2968125000002</v>
+      </c>
+      <c r="BK20">
+        <f>IF(ISBLANK(A20), "", IF(BC20="wet", $BS$8, $BS$9))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BL20">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM20">
+        <f t="shared" si="36"/>
+        <v>2.680771058035715E-2</v>
+      </c>
+      <c r="BN20">
+        <f t="shared" si="34"/>
+        <v>8.935903526785716E-3</v>
+      </c>
+      <c r="BO20">
+        <f>SUM(BM20:BM23)</f>
+        <v>8.8741014685351033E-2</v>
+      </c>
+      <c r="BP20">
+        <f>SUM(BN20:BN23)</f>
+        <v>2.9580338228450343E-2</v>
+      </c>
+      <c r="BR20" t="s">
+        <v>20</v>
+      </c>
+      <c r="BS20">
+        <v>2.9000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>556</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>551</v>
+      </c>
+      <c r="F21">
+        <v>600</v>
+      </c>
+      <c r="G21">
+        <v>200</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="4"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="5"/>
+        <v>0.46</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="6"/>
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0.5</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0.5</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>5880</v>
+      </c>
+      <c r="U21">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="X21">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="Z21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="2"/>
+        <v>2940</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <f t="shared" si="2"/>
+        <v>2940</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK21">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL21">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM21">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO21">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ21">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR21">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS21">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <f t="shared" si="3"/>
+        <v>2940</v>
+      </c>
+      <c r="AV21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <f t="shared" si="3"/>
+        <v>2199.12</v>
+      </c>
+      <c r="AX21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <f t="shared" si="25"/>
+        <v>5139.12</v>
+      </c>
+      <c r="AZ21">
+        <f t="shared" si="26"/>
+        <v>2940</v>
+      </c>
+      <c r="BA21">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <f t="shared" si="27"/>
+        <v>2199.12</v>
+      </c>
+      <c r="BC21" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD21">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF21">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0.75</v>
+      </c>
+      <c r="BH21">
+        <f t="shared" si="31"/>
+        <v>3522.12</v>
+      </c>
+      <c r="BI21">
+        <f t="shared" si="32"/>
+        <v>2641.59</v>
+      </c>
+      <c r="BJ21">
+        <f t="shared" si="33"/>
+        <v>880.53</v>
+      </c>
+      <c r="BK21">
+        <f>IF(ISBLANK(A21), "", IF(BC21="wet", $BS$8, $BS$9))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BL21">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM21">
+        <f t="shared" si="36"/>
+        <v>2.0755349999999999E-2</v>
+      </c>
+      <c r="BN21">
+        <f t="shared" si="34"/>
+        <v>6.9184500000000005E-3</v>
+      </c>
+      <c r="BR21" t="s">
+        <v>21</v>
+      </c>
+      <c r="BS21">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>556</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="D22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>552</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="G22">
+        <v>299</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="4"/>
+        <v>2.5</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="5"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="6"/>
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K22">
+        <v>0.3</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0.3</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0.4</v>
+      </c>
+      <c r="Q22" t="b">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.25</v>
+      </c>
+      <c r="T22">
+        <v>1375.3999999999999</v>
+      </c>
+      <c r="U22">
+        <f t="shared" si="7"/>
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <f t="shared" si="9"/>
+        <v>0.3</v>
+      </c>
+      <c r="Y22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <f t="shared" si="10"/>
+        <v>0.47500000000000003</v>
+      </c>
+      <c r="AA22">
+        <f t="shared" si="11"/>
+        <v>309.46499999999992</v>
+      </c>
+      <c r="AB22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="2"/>
+        <v>412.61999999999995</v>
+      </c>
+      <c r="AE22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="2"/>
+        <v>653.31499999999994</v>
+      </c>
+      <c r="AG22">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH22">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI22">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK22">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL22">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM22">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO22">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ22">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR22">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS22">
+        <f t="shared" si="24"/>
+        <v>139.25924999999995</v>
+      </c>
+      <c r="AT22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <f t="shared" si="3"/>
+        <v>356.91629999999998</v>
+      </c>
+      <c r="AW22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <f t="shared" si="3"/>
+        <v>519.38542499999994</v>
+      </c>
+      <c r="AY22">
+        <f t="shared" si="25"/>
+        <v>1015.5609749999999</v>
+      </c>
+      <c r="AZ22">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <f t="shared" si="26"/>
+        <v>356.91629999999998</v>
+      </c>
+      <c r="BB22">
+        <f t="shared" si="27"/>
+        <v>658.64467499999989</v>
+      </c>
+      <c r="BC22" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD22">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF22">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0.75</v>
+      </c>
+      <c r="BH22">
+        <f t="shared" si="31"/>
+        <v>942.39313349999986</v>
+      </c>
+      <c r="BI22">
+        <f t="shared" si="32"/>
+        <v>706.79485012499993</v>
+      </c>
+      <c r="BJ22">
+        <f t="shared" si="33"/>
+        <v>235.59828337499997</v>
+      </c>
+      <c r="BK22">
+        <f>IF(ISBLANK(A22), "", IF(BC22="wet", $BS$8, $BS$9))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BL22">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM22">
+        <f t="shared" si="36"/>
+        <v>5.5533881081249997E-3</v>
+      </c>
+      <c r="BN22">
+        <f t="shared" si="34"/>
+        <v>1.8511293693749997E-3</v>
+      </c>
+      <c r="BR22" t="s">
+        <v>15</v>
+      </c>
+      <c r="BS22">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>556</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>553</v>
+      </c>
+      <c r="F23">
+        <v>999</v>
+      </c>
+      <c r="G23">
+        <v>299</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="4"/>
+        <v>1.71</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="5"/>
+        <v>0.39</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="6"/>
+        <v>3.1232876712328769E-2</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0.5</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0.5</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>0.25</v>
+      </c>
+      <c r="S23">
+        <v>0.25</v>
+      </c>
+      <c r="T23">
+        <v>9329.2915068493148</v>
+      </c>
+      <c r="U23">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="X23">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <f t="shared" si="1"/>
+        <v>0.375</v>
+      </c>
+      <c r="Z23">
+        <f t="shared" si="10"/>
+        <v>0.25</v>
+      </c>
+      <c r="AA23">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <f t="shared" si="2"/>
+        <v>3498.4843150684928</v>
+      </c>
+      <c r="AD23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <f t="shared" si="2"/>
+        <v>3498.4843150684928</v>
+      </c>
+      <c r="AF23">
+        <f t="shared" si="2"/>
+        <v>2332.3228767123287</v>
+      </c>
+      <c r="AG23">
+        <f t="shared" si="12"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH23">
+        <f t="shared" si="13"/>
+        <v>0.3</v>
+      </c>
+      <c r="AI23">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <f t="shared" si="15"/>
+        <v>0.125</v>
+      </c>
+      <c r="AK23">
+        <f t="shared" si="16"/>
+        <v>0.25</v>
+      </c>
+      <c r="AL23">
+        <f t="shared" si="17"/>
+        <v>0.2</v>
+      </c>
+      <c r="AM23">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <f t="shared" si="19"/>
+        <v>0.02</v>
+      </c>
+      <c r="AO23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <f t="shared" si="21"/>
+        <v>0.01</v>
+      </c>
+      <c r="AQ23">
+        <f t="shared" si="22"/>
+        <v>2E-3</v>
+      </c>
+      <c r="AR23">
+        <f t="shared" si="23"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AS23">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <f t="shared" si="3"/>
+        <v>3498.4843150684928</v>
+      </c>
+      <c r="AV23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <f t="shared" si="3"/>
+        <v>2616.8662676712324</v>
+      </c>
+      <c r="AX23">
+        <f t="shared" si="3"/>
+        <v>1854.1966869863013</v>
+      </c>
+      <c r="AY23">
+        <f t="shared" si="25"/>
+        <v>7969.5472697260266</v>
+      </c>
+      <c r="AZ23">
+        <f t="shared" si="26"/>
+        <v>3498.4843150684928</v>
+      </c>
+      <c r="BA23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <f t="shared" si="27"/>
+        <v>4471.0629546575337</v>
+      </c>
+      <c r="BC23" t="s">
+        <v>19</v>
+      </c>
+      <c r="BD23">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <f t="shared" si="29"/>
+        <v>0.02</v>
+      </c>
+      <c r="BF23">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0.75</v>
+      </c>
+      <c r="BH23">
+        <f t="shared" si="31"/>
+        <v>6045.3808964383552</v>
+      </c>
+      <c r="BI23">
+        <f t="shared" si="32"/>
+        <v>4534.0356723287659</v>
+      </c>
+      <c r="BJ23">
+        <f t="shared" si="33"/>
+        <v>1511.3452241095888</v>
+      </c>
+      <c r="BK23">
+        <f>IF(ISBLANK(A23), "", IF(BC23="wet", $BS$8, $BS$9))</f>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="BL23">
+        <f t="shared" si="35"/>
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="BM23">
+        <f t="shared" si="36"/>
+        <v>3.5624565996868876E-2</v>
+      </c>
+      <c r="BN23">
+        <f t="shared" si="34"/>
+        <v>1.1874855332289627E-2</v>
+      </c>
+      <c r="BR23" t="s">
+        <v>23</v>
+      </c>
+      <c r="BS23">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BK24" t="str">
+        <f>IF(ISBLANK(A24), "", IF(BC24="wet", $BS$8, $BS$9))</f>
+        <v/>
+      </c>
+      <c r="BR24" t="s">
+        <v>22</v>
+      </c>
+      <c r="BS24">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BK25" t="str">
+        <f>IF(ISBLANK(A25), "", IF(BC25="wet", $BS$8, $BS$9))</f>
+        <v/>
+      </c>
+      <c r="BR25" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS25">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BI26" t="str">
+        <f>IF(ISBLANK(A24), "", (Y24*(1-P24-R24)-X24)*F24)</f>
+        <v/>
+      </c>
+      <c r="BJ26" t="str">
+        <f>IF(ISBLANK(A24), "", (Y24*(1-P24-R24)-X24)*(1 -F24))</f>
+        <v/>
+      </c>
+      <c r="BK26" t="str">
+        <f>IF(ISBLANK(A24), "", IF(D24="wet", $BS$8, $BS$9))</f>
+        <v/>
+      </c>
+      <c r="BL26" t="str">
+        <f>IF(ISBLANK(A24), "", $BS$12)</f>
+        <v/>
+      </c>
+      <c r="BM26" t="str">
+        <f>IF(ISBLANK(A24), "", BI26*BK26*BL26 / 1000)</f>
+        <v/>
+      </c>
+      <c r="BN26" t="str">
+        <f>IF(ISBLANK(B24), "", BJ26*BK26*BL26 / 1000)</f>
+        <v/>
+      </c>
+      <c r="BO26" t="str">
+        <f>IF(ISBLANK(A24), "", BM26+BM27)</f>
+        <v/>
+      </c>
+      <c r="BP26" t="str">
+        <f>IF(ISBLANK(A24), "", BN26+BN27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BI27" t="str">
+        <f>IF(ISBLANK(A24), "", (Y25*(1-P25-R25)-X25)*F24)</f>
+        <v/>
+      </c>
+      <c r="BJ27" t="str">
+        <f>IF(ISBLANK(A24), "", (Y25*(1-P25-R25)-X25)*(1 - F24))</f>
+        <v/>
+      </c>
+      <c r="BK27" t="str">
+        <f>IF(ISBLANK(A24), "", IF(D24="wet", $BS$8, $BS$9))</f>
+        <v/>
+      </c>
+      <c r="BL27" t="str">
+        <f>IF(ISBLANK(A24), "", $BS$12)</f>
+        <v/>
+      </c>
+      <c r="BM27" t="str">
+        <f>IF(ISBLANK(A24), "", BI27*BK27*BL27 / 1000)</f>
+        <v/>
+      </c>
+      <c r="BN27" t="str">
+        <f>IF(ISBLANK(A24), "", BJ27*BK27*BL27 / 1000)</f>
+        <v/>
+      </c>
+      <c r="BO27" t="str">
+        <f>IF(ISBLANK(A25), "", BI27*BK27*BL27 / 1000)</f>
+        <v/>
+      </c>
+      <c r="BR27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BR28" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BR29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BR30" t="s">
+        <v>86</v>
+      </c>
+      <c r="BS30">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="31" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BR31" t="s">
+        <v>78</v>
+      </c>
+      <c r="BS31">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="32" spans="1:71" x14ac:dyDescent="0.2">
+      <c r="BR32" t="s">
+        <v>81</v>
+      </c>
+      <c r="BS32">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR33" t="s">
+        <v>89</v>
+      </c>
+      <c r="BS33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR34" t="s">
+        <v>91</v>
+      </c>
+      <c r="BS34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR35" t="s">
+        <v>79</v>
+      </c>
+      <c r="BS35">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR37" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR39" t="s">
+        <v>86</v>
+      </c>
+      <c r="BS39">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="40" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR40" t="s">
+        <v>78</v>
+      </c>
+      <c r="BS40">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="41" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR41" t="s">
+        <v>81</v>
+      </c>
+      <c r="BS41">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="42" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR42" t="s">
+        <v>89</v>
+      </c>
+      <c r="BS42">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="43" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR43" t="s">
+        <v>91</v>
+      </c>
+      <c r="BS43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR44" t="s">
+        <v>79</v>
+      </c>
+      <c r="BS44">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="46" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR46" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="47" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR47" t="s">
+        <v>561</v>
+      </c>
+      <c r="BS47" t="s">
+        <v>562</v>
+      </c>
+      <c r="BT47" t="s">
+        <v>563</v>
+      </c>
+      <c r="BU47" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="48" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR48" t="s">
+        <v>550</v>
+      </c>
+      <c r="BS48">
+        <v>2.62</v>
+      </c>
+      <c r="BT48">
+        <v>0.4</v>
+      </c>
+      <c r="BU48">
+        <v>4.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR49" t="s">
+        <v>551</v>
+      </c>
+      <c r="BS49">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="BT49">
+        <v>0.46</v>
+      </c>
+      <c r="BU49">
+        <v>4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR50" t="s">
+        <v>552</v>
+      </c>
+      <c r="BS50">
+        <v>2.5</v>
+      </c>
+      <c r="BT50">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="BU50">
+        <v>4.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="70:73" x14ac:dyDescent="0.2">
+      <c r="BR51" t="s">
+        <v>553</v>
+      </c>
+      <c r="BS51">
+        <v>1.71</v>
+      </c>
+      <c r="BT51">
+        <v>0.39</v>
+      </c>
+      <c r="BU51">
+        <f>11.4/365</f>
+        <v>3.1232876712328769E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AN40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -6181,7 +11167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:CH96"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -17856,7 +22842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A4:BO66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -18670,7 +23656,7 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <f t="shared" ref="AA12:AA14" si="4">SUM(W13:Z13)</f>
+        <f t="shared" ref="AA13:AA14" si="4">SUM(W13:Z13)</f>
         <v>35.487791999999999</v>
       </c>
       <c r="AF13" s="5" t="s">
